--- a/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day2.xlsx
+++ b/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dadi2\OneDrive\문서\카카오톡 받은 파일\사운드 다이얼로그 수정\사운드 다이얼로그\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gksk7\Desktop\Download\Download\Assets\Resources\4. Data\1. VisualNovel\Dialogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA5E915-4EAF-482B-8831-9EC840D85C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FC75E3-6EE0-449C-BC72-0BA68734D1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" tabRatio="760" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="760" firstSheet="17" activeTab="25" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
   </bookViews>
   <sheets>
     <sheet name="S00_1_SchoolGo" sheetId="2" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3203" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3208" uniqueCount="786">
   <si>
     <t>dialogType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -11105,9 +11105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{SA04}</t>
-  </si>
-  <si>
     <t>MI04</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -11156,6 +11153,14 @@
   </si>
   <si>
     <t>effect</t>
+  </si>
+  <si>
+    <t>EF13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -13212,9 +13217,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -13252,7 +13257,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -13358,7 +13363,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -13500,7 +13505,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -13509,7 +13514,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2492B5-5286-4C51-A0EE-617DAAF7402C}">
   <dimension ref="A1:T72"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
     <col min="3" max="3" width="9.875" customWidth="1"/>
@@ -13556,10 +13561,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -13603,7 +13608,7 @@
       <c r="S2" s="38"/>
       <c r="T2"/>
     </row>
-    <row r="3" spans="1:20" ht="26.05" customHeight="1">
+    <row r="3" spans="1:20" ht="26.1" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -13624,7 +13629,7 @@
       <c r="S3" s="38"/>
       <c r="T3"/>
     </row>
-    <row r="4" spans="1:20" ht="31.2" customHeight="1">
+    <row r="4" spans="1:20" ht="31.15" customHeight="1">
       <c r="A4">
         <v>1</v>
       </c>
@@ -13645,7 +13650,7 @@
       <c r="S4" s="38"/>
       <c r="T4"/>
     </row>
-    <row r="5" spans="1:20" ht="26.05" customHeight="1">
+    <row r="5" spans="1:20" ht="26.1" customHeight="1">
       <c r="A5">
         <v>1</v>
       </c>
@@ -13708,7 +13713,7 @@
       <c r="S7" s="38"/>
       <c r="T7"/>
     </row>
-    <row r="8" spans="1:20" ht="28.2" customHeight="1">
+    <row r="8" spans="1:20" ht="28.15" customHeight="1">
       <c r="A8">
         <v>1</v>
       </c>
@@ -13729,7 +13734,7 @@
       <c r="S8" s="38"/>
       <c r="T8"/>
     </row>
-    <row r="9" spans="1:20" ht="29.95" customHeight="1">
+    <row r="9" spans="1:20" ht="30" customHeight="1">
       <c r="A9">
         <v>1</v>
       </c>
@@ -14685,7 +14690,7 @@
         <v>669</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K50"/>
       <c r="S50" s="38"/>
@@ -15186,7 +15191,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACFB045D-9DEA-4213-951B-B6C6659A4BD9}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="18.125" customWidth="1"/>
     <col min="6" max="6" width="56.25" customWidth="1"/>
@@ -15225,10 +15230,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -15478,7 +15483,7 @@
         <v>682</v>
       </c>
       <c r="J12" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -15784,7 +15789,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB216B21-F13B-4AEF-B2E5-65437E24D49A}">
   <dimension ref="A1:S49"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
     <col min="5" max="5" width="16.25" customWidth="1"/>
@@ -15824,10 +15829,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -16048,8 +16053,8 @@
       <c r="G13" t="s">
         <v>667</v>
       </c>
-      <c r="J13" s="38">
-        <v>13</v>
+      <c r="J13" s="38" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -16103,7 +16108,7 @@
         <v>683</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -16126,7 +16131,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="24.25">
+    <row r="18" spans="1:8" ht="24">
       <c r="A18">
         <v>1</v>
       </c>
@@ -16366,7 +16371,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="24.25">
+    <row r="30" spans="1:8" ht="24">
       <c r="A30">
         <v>1</v>
       </c>
@@ -16446,7 +16451,7 @@
         <v>685</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -16469,7 +16474,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="24.25">
+    <row r="35" spans="1:10" ht="24">
       <c r="A35">
         <v>1</v>
       </c>
@@ -16609,7 +16614,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="24.25">
+    <row r="42" spans="1:10" ht="24">
       <c r="A42">
         <v>1</v>
       </c>
@@ -16709,7 +16714,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="24.25">
+    <row r="47" spans="1:10" ht="24">
       <c r="A47">
         <v>1</v>
       </c>
@@ -16817,7 +16822,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E14DDB-7C1C-43B8-BB3C-0CE6BC539040}">
   <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="16.75" customWidth="1"/>
     <col min="6" max="6" width="57.25" customWidth="1"/>
@@ -16856,10 +16861,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -17126,7 +17131,7 @@
         <v>746</v>
       </c>
       <c r="J13" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -17380,7 +17385,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106A4C8D-BFB9-4E65-8DB1-E1FDE07EB2CE}">
   <dimension ref="A1:R10"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="13.25" customWidth="1"/>
     <col min="6" max="6" width="40.625" customWidth="1"/>
@@ -17419,10 +17424,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -17680,7 +17685,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE6FF71E-D6D4-45AA-8EB7-6EFB05DDBC98}">
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="49.25" customWidth="1"/>
@@ -17724,10 +17729,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -17774,7 +17779,7 @@
         <v>684</v>
       </c>
       <c r="J2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -18002,7 +18007,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B67B17-9B8E-4E8E-AEC1-F9AD948F1739}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="48.375" customWidth="1"/>
@@ -18043,10 +18048,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -18176,7 +18181,7 @@
         <v>684</v>
       </c>
       <c r="J6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -18356,7 +18361,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71FE0-0D17-4E61-A836-54535D7026D7}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="14.5" customWidth="1"/>
     <col min="6" max="6" width="55.125" customWidth="1"/>
@@ -18396,10 +18401,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -18726,7 +18731,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD30F93-B3C9-48E4-BAEB-257DAFEB982C}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="60.25" customWidth="1"/>
@@ -18767,10 +18772,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -18960,7 +18965,7 @@
         <v>687</v>
       </c>
       <c r="J9" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -19123,7 +19128,7 @@
         <v>747</v>
       </c>
       <c r="J17" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -19243,7 +19248,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF51896-F2C3-4A8C-8F8A-87F736BAAB5C}">
   <dimension ref="A1:S38"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="63.75" customWidth="1"/>
@@ -19283,10 +19288,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -19372,7 +19377,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="24.25">
+    <row r="6" spans="1:18" ht="24">
       <c r="A6">
         <v>1</v>
       </c>
@@ -19886,7 +19891,7 @@
         <v>689</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -20117,7 +20122,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A068B11-DAA2-4778-8524-27CDD74C9114}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="17.75" customWidth="1"/>
     <col min="6" max="6" width="57.375" customWidth="1"/>
@@ -20159,10 +20164,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -20249,7 +20254,7 @@
         <v>689</v>
       </c>
       <c r="J4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -20500,7 +20505,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABE6EEA-441F-4145-BD21-BED610835A4E}">
   <dimension ref="A1:S77"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="65.75" customWidth="1"/>
@@ -20542,10 +20547,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -20863,8 +20868,8 @@
       <c r="G18" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="38">
-        <v>13</v>
+      <c r="J18" s="38" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -20901,7 +20906,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -20944,7 +20949,7 @@
         <v>670</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -21067,7 +21072,7 @@
         <v>670</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -21249,8 +21254,8 @@
       <c r="H37" t="s">
         <v>670</v>
       </c>
-      <c r="J37" s="38">
-        <v>11</v>
+      <c r="J37" s="38" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -22094,7 +22099,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD8781FC-B5FB-4BDC-A6AC-E7EDE4A10B60}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="19.25" customWidth="1"/>
     <col min="6" max="6" width="66.75" customWidth="1"/>
@@ -22133,10 +22138,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -22431,7 +22436,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F938C4-24DF-44A8-AF3D-8C9C401C0375}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="37.625" customWidth="1"/>
@@ -22469,10 +22474,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -22642,7 +22647,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF294853-A5F1-4462-8BE4-E4D9EF238D75}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="18.75" customWidth="1"/>
     <col min="6" max="6" width="62" customWidth="1"/>
@@ -22678,10 +22683,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -22951,7 +22956,7 @@
         <v>691</v>
       </c>
       <c r="J13" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -23068,7 +23073,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3424D189-B25E-4117-AB1E-5CE6E0D68D03}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.25" customWidth="1"/>
     <col min="6" max="6" width="80.125" customWidth="1"/>
@@ -23104,10 +23109,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -23497,7 +23502,7 @@
         <v>693</v>
       </c>
       <c r="J19" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -23574,7 +23579,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D91E1F32-C105-4B60-A873-DAA120B7C3B6}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="12.25" customWidth="1"/>
     <col min="6" max="6" width="57.75" customWidth="1"/>
@@ -23610,10 +23615,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -23866,7 +23871,7 @@
         <v>688</v>
       </c>
       <c r="J12" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -24259,7 +24264,7 @@
         <v>755</v>
       </c>
       <c r="J33" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -24356,7 +24361,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52CED-8D2E-4744-8A59-535CFF1C067F}">
   <dimension ref="A1:R87"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
@@ -24391,10 +24396,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -24452,7 +24457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="27.1">
+    <row r="4" spans="1:18" ht="25.5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -24511,8 +24516,8 @@
       <c r="H6" t="s">
         <v>700</v>
       </c>
-      <c r="J6">
-        <v>13</v>
+      <c r="J6" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -24654,8 +24659,8 @@
       <c r="H13" t="s">
         <v>702</v>
       </c>
-      <c r="J13">
-        <v>13</v>
+      <c r="J13" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -24818,7 +24823,7 @@
         <v>702</v>
       </c>
       <c r="J21" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -24841,7 +24846,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="24.25">
+    <row r="23" spans="1:10" ht="24">
       <c r="A23">
         <v>1</v>
       </c>
@@ -25101,7 +25106,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="24.25">
+    <row r="36" spans="1:10" ht="24">
       <c r="A36">
         <v>1</v>
       </c>
@@ -25161,7 +25166,7 @@
         <v>753</v>
       </c>
       <c r="J38" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -25384,7 +25389,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="29.95">
+    <row r="50" spans="1:8" ht="27">
       <c r="A50">
         <v>1</v>
       </c>
@@ -25464,7 +25469,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="24.25">
+    <row r="54" spans="1:8" ht="24">
       <c r="A54">
         <v>1</v>
       </c>
@@ -25564,7 +25569,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="24.25">
+    <row r="59" spans="1:8" ht="24">
       <c r="A59">
         <v>1</v>
       </c>
@@ -26168,7 +26173,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E129760B-D16C-4E2A-B7A4-F67A51649F7A}">
   <dimension ref="A1:R64"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="21.375" customWidth="1"/>
     <col min="6" max="6" width="62.375" customWidth="1"/>
@@ -26202,10 +26207,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -26725,7 +26730,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="24.25">
+    <row r="31" spans="1:9" ht="24">
       <c r="A31">
         <v>1</v>
       </c>
@@ -26810,7 +26815,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="299.39999999999998">
+    <row r="36" spans="1:7" ht="256.5">
       <c r="A36">
         <v>1</v>
       </c>
@@ -27348,7 +27353,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F6D56-6BF4-472D-8231-C335D914875C}">
   <dimension ref="A1:S27"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="91.75" customWidth="1"/>
@@ -27389,10 +27394,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -27530,7 +27535,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -27673,7 +27678,7 @@
         <v>675</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -27984,7 +27989,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30CFF362-6F10-4AE0-BC32-774B7564766B}">
   <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="63.75" customWidth="1"/>
@@ -28023,10 +28028,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -28153,7 +28158,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="24.25">
+    <row r="7" spans="1:18" ht="24">
       <c r="A7">
         <v>1</v>
       </c>
@@ -28624,7 +28629,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A41BF28-BF73-45B4-A6FE-839359A62393}">
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="12.625" customWidth="1"/>
     <col min="6" max="6" width="59.875" customWidth="1"/>
@@ -28663,10 +28668,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -28713,7 +28718,7 @@
         <v>675</v>
       </c>
       <c r="J2" s="38" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -28756,7 +28761,7 @@
         <v>676</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -28959,7 +28964,7 @@
         <v>669</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -29113,7 +29118,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29187108-CC33-4637-A601-47A2B875A65F}">
   <dimension ref="A1:S45"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="14.5" customWidth="1"/>
     <col min="6" max="6" width="53.75" customWidth="1"/>
@@ -29152,10 +29157,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" s="38" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -29302,7 +29307,7 @@
         <v>669</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -30037,7 +30042,7 @@
         <v>669</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -30191,7 +30196,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13023BAD-E986-4D03-80A9-6D8865BF77C8}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="14.75" customWidth="1"/>
     <col min="6" max="6" width="68" customWidth="1"/>
@@ -30232,10 +30237,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -30262,7 +30267,7 @@
         <v>19</v>
       </c>
       <c r="S1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -30479,7 +30484,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105F8B61-6BD9-41CC-A526-0E7EDA814A6F}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.125" customWidth="1"/>
     <col min="6" max="6" width="59.5" customWidth="1"/>
@@ -30518,10 +30523,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -30711,7 +30716,7 @@
         <v>675</v>
       </c>
       <c r="J9" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -30797,7 +30802,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE62B79-AA0F-4591-909D-5913DC2D14C2}">
   <dimension ref="A1:R10"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="69.25" customWidth="1"/>
@@ -30836,10 +30841,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1" t="s">
         <v>783</v>
-      </c>
-      <c r="J1" t="s">
-        <v>784</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -30966,7 +30971,7 @@
         <v>673</v>
       </c>
       <c r="J6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7" spans="1:18">
